--- a/ig/DM-OCTOBRE-2026/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2026/ASS-X04-CorrespondanceType-Classe-CISIS.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="195">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -458,6 +458,12 @@
     <t>101881-1</t>
   </si>
   <si>
+    <t>85895-1</t>
+  </si>
+  <si>
+    <t>104144-1</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A05-TypeDocComplementaire/FHIR/TRE-A05-TypeDocComplementaire</t>
   </si>
   <si>
@@ -579,6 +585,9 @@
   </si>
   <si>
     <t>FICHE-CONTACTS</t>
+  </si>
+  <si>
+    <t>JUSTIF-PRESC-RENF</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_A12-NomenclatureASTM/FHIR/TRE-A12-NomenclatureASTM</t>
@@ -860,7 +869,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2235,6 +2244,32 @@
         <v>37</v>
       </c>
       <c r="E105" s="2"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B106" s="2"/>
+      <c r="C106" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E106" s="2"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B107" s="2"/>
+      <c r="C107" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E107" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2243,7 +2278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2265,7 +2300,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2282,7 +2317,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
@@ -2295,7 +2330,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -2308,7 +2343,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -2321,7 +2356,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -2334,7 +2369,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -2347,7 +2382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -2360,7 +2395,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -2373,7 +2408,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
@@ -2386,7 +2421,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
@@ -2399,7 +2434,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -2412,7 +2447,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -2425,7 +2460,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -2438,7 +2473,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -2451,7 +2486,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -2464,7 +2499,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -2477,7 +2512,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -2490,7 +2525,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -2503,7 +2538,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -2516,7 +2551,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -2529,7 +2564,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -2542,7 +2577,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -2555,7 +2590,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -2568,7 +2603,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -2581,7 +2616,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -2594,7 +2629,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -2607,7 +2642,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -2620,20 +2655,20 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -2646,7 +2681,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -2659,7 +2694,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -2672,7 +2707,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -2685,7 +2720,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -2698,7 +2733,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -2711,7 +2746,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -2724,7 +2759,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -2737,7 +2772,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -2750,20 +2785,20 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -2773,6 +2808,19 @@
         <v>78</v>
       </c>
       <c r="E40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E41" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -2803,7 +2851,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -2812,7 +2860,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -2820,14 +2868,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E3" s="2"/>
     </row>
